--- a/ig/nr-rm-interpretation-binding/CodeSystem-fr-core-identifier-type.xlsx
+++ b/ig/nr-rm-interpretation-binding/CodeSystem-fr-core-identifier-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T10:17:35+00:00</t>
+    <t>2023-10-09T10:19:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
